--- a/workflows/weekly-ops-advice-flow/out/周度汇总.xlsx
+++ b/workflows/weekly-ops-advice-flow/out/周度汇总.xlsx
@@ -837,17 +837,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
@@ -913,22 +913,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周二</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>营收连续趋势</t>
+          <t>营收环比</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R3 连续趋势</t>
+          <t>R1 绝对阈值</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -938,17 +938,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>连续 4 天下滑</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>连续 ≥ 3 天 且 累计 &gt; 10%</t>
+          <t>环比 ≤ -20%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-05 → 2026-09-09 累计 -23.1%</t>
+          <t>营收 6247 元（前一日 8929 元）</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -958,54 +958,54 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-29.8%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周六</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>转化率连续趋势</t>
+          <t>营收环比</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>R3 连续趋势</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>R1 绝对阈值</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>连续 4 天下滑</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>连续 ≥ 3 天 且 累计 &gt; 10%</t>
+          <t>环比 ≤ -20%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-08 → 2026-09-12 累计 -30.7%</t>
+          <t>营收 8929 元（前一日 11621 元）</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>营收同比</t>
+          <t>营收离群</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>R4 季节性（同比优先）</t>
+          <t>R2 离群（Z-score(2σ)）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1052,17 +1052,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>6247元</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>同比偏离 ≥ 20%</t>
+          <t>|x-μ| &gt; 2σ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>去年同期 11922 元，本期 8942 元</t>
+          <t>Z=-2.30（μ=9521.8，σ=1423.8）</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1072,29 +1072,29 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+3.3%</t>
+          <t>-29.8%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周六</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>营收环比</t>
+          <t>退款率</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1109,17 +1109,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>6.79%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>环比 ≤ -20%</t>
+          <t>&gt; 5.0%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>营收 6895 元（前一日 8679 元）</t>
+          <t>退款 624 元 / 营收 9184 元</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1129,12 +1129,69 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>+4.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>退款率离群</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>R2 离群（Z-score(2σ)）</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6.79%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>|x-μ| &gt; 2σ</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Z=+3.62（μ=2.7，σ=1.1）</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>确认异常</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>+1.7%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>+4.8%</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1233,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>让店长 王敏把「2026-09-09 营收连续趋势（连续 4 天下滑）」当作下周第一件事：拉出该指标对应的原始单据逐条核对，先定性再动手。（零预算：不动用投放费用）</t>
+          <t>让店长 王敏把「2026-09-08 营收环比（-30.0%）」当作下周第一件事：拉出该指标对应的原始单据逐条核对，先定性再动手。（零预算：不动用投放费用）</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1245,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>本周存在 2 条高等级确认异常，优先级最高</t>
+          <t>本周存在 1 条高等级确认异常，优先级最高</t>
         </is>
       </c>
     </row>

--- a/workflows/weekly-ops-advice-flow/out/周度汇总.xlsx
+++ b/workflows/weekly-ops-advice-flow/out/周度汇总.xlsx
@@ -837,17 +837,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
@@ -913,22 +913,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>营收环比</t>
+          <t>营收连续趋势</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R1 绝对阈值</t>
+          <t>R3 连续趋势</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -938,17 +938,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>连续 4 天下滑</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>环比 ≤ -20%</t>
+          <t>连续 ≥ 3 天 且 累计 &gt; 10%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>营收 6247 元（前一日 8929 元）</t>
+          <t>2026-09-05 → 2026-09-09 累计 -23.1%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -958,54 +958,54 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-2.3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周六</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>营收环比</t>
+          <t>转化率连续趋势</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>R1 绝对阈值</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R3 连续趋势</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>连续 4 天下滑</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>环比 ≤ -20%</t>
+          <t>连续 ≥ 3 天 且 累计 &gt; 10%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>营收 8929 元（前一日 11621 元）</t>
+          <t>2026-09-08 → 2026-09-12 累计 -30.7%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-38.9%</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>营收离群</t>
+          <t>营收同比</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>R2 离群（Z-score(2σ)）</t>
+          <t>R4 季节性（同比优先）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1052,17 +1052,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>6247元</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>|x-μ| &gt; 2σ</t>
+          <t>同比偏离 ≥ 20%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Z=-2.30（μ=9521.8，σ=1423.8）</t>
+          <t>去年同期 11922 元，本期 8942 元</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1072,29 +1072,29 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>+3.3%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周六</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>退款率</t>
+          <t>营收环比</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1109,17 +1109,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6.79%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>&gt; 5.0%</t>
+          <t>环比 ≤ -20%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>退款 624 元 / 营收 9184 元</t>
+          <t>营收 6895 元（前一日 8679 元）</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1129,69 +1129,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+4.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>周三</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>退款率离群</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>R2 离群（Z-score(2σ)）</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>6.79%</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>|x-μ| &gt; 2σ</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Z=+3.62（μ=2.7，σ=1.1）</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>确认异常</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>+1.7%</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>+4.8%</t>
+          <t>-38.9%</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>让店长 王敏把「2026-09-08 营收环比（-30.0%）」当作下周第一件事：拉出该指标对应的原始单据逐条核对，先定性再动手。（零预算：不动用投放费用）</t>
+          <t>让店长 王敏把「2026-09-09 营收连续趋势（连续 4 天下滑）」当作下周第一件事：拉出该指标对应的原始单据逐条核对，先定性再动手。（零预算：不动用投放费用）</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1188,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>本周存在 1 条高等级确认异常，优先级最高</t>
+          <t>本周存在 2 条高等级确认异常，优先级最高</t>
         </is>
       </c>
     </row>
